--- a/ResourcesBD/Excel_Validation.xlsx
+++ b/ResourcesBD/Excel_Validation.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6930"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7350"/>
   </bookViews>
   <sheets>
     <sheet name="Excel Template" sheetId="1" r:id="rId1"/>
@@ -21,46 +21,44 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
-    <t>Product</t>
-  </si>
-  <si>
-    <t>Restriction From</t>
-  </si>
-  <si>
-    <t>Restriction To</t>
-  </si>
-  <si>
-    <t>Date From</t>
-  </si>
-  <si>
-    <t>Date To</t>
-  </si>
-  <si>
-    <t>2027-06-17</t>
-  </si>
-  <si>
-    <t>2027-06-27</t>
-  </si>
-  <si>
-    <t>20042975</t>
+    <t>Product*</t>
+  </si>
+  <si>
+    <t>Restriction From*</t>
+  </si>
+  <si>
+    <t>Restriction To*</t>
+  </si>
+  <si>
+    <t>Date From*</t>
+  </si>
+  <si>
+    <t>Date To*</t>
+  </si>
+  <si>
+    <t>20099831</t>
+  </si>
+  <si>
+    <t>2026-07-01</t>
+  </si>
+  <si>
+    <t>2027-07-02</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
+  </numFmts>
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -87,7 +85,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -371,11 +369,11 @@
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="18.81640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.1796875" style="2" customWidth="1"/>
+    <col min="1" max="1" width="8.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.54296875" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.26953125" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.54296875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.453125" customWidth="1"/>
+    <col min="4" max="4" width="10.54296875" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.08984375" style="3" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="8" style="1"/>
   </cols>
   <sheetData>
@@ -389,32 +387,31 @@
       <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="2">
+        <v>500</v>
+      </c>
+      <c r="C2" s="2">
+        <v>50000</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>7</v>
-      </c>
-      <c r="B2" s="2">
-        <v>9999</v>
-      </c>
-      <c r="C2" s="2">
-        <v>10000</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>6</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>